--- a/FastTest PlugIn - DataBase.xlsx
+++ b/FastTest PlugIn - DataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28422"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milag\Desktop\FastTest_PlugIn_V78\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AHGM\0. GITHUB\FTP_Privado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3EF5B0-154E-4866-863E-259C1913984A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5E8E5F-5049-4F13-9556-962991C93082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12266" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INICIO" sheetId="6" r:id="rId1"/>
@@ -3194,14 +3194,14 @@
 默认情况下，根据您要使用的语言编写相应的数字。 您可以随时更改它。</t>
   </si>
   <si>
-    <t>V - 7.8  - 02/04/2023</t>
+    <t>V - 8.3  - 02/01/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3367,14 +3367,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFE87B00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4350,7 +4342,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -4527,11 +4519,11 @@
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -4551,51 +4543,51 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4622,7 +4614,7 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4640,7 +4632,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4652,7 +4644,7 @@
     <xf numFmtId="0" fontId="12" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4674,7 +4666,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4683,10 +4675,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4746,7 +4738,7 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4755,10 +4747,10 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4886,11 +4878,11 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4902,8 +4894,8 @@
     <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4931,6 +4923,50 @@
   <dxfs count="348">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -5967,36 +6003,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -7780,20 +7786,6 @@
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor rgb="FF005877"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -20549,54 +20541,54 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabla_Menu" displayName="Tabla_Menu" ref="S2:AF30" totalsRowCount="1" headerRowDxfId="40" dataDxfId="39" tableBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabla_Menu" displayName="Tabla_Menu" ref="S2:AF30" totalsRowCount="1" headerRowDxfId="45" dataDxfId="44" tableBorderDxfId="43">
   <autoFilter ref="S2:AF29" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="N Sub" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="36">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="N Sub" totalsRowFunction="custom" dataDxfId="42" totalsRowDxfId="41">
       <calculatedColumnFormula>IF(Tabla_Menu[[#This Row],[Nivel]]=T2,0,COUNTIF(Tabla_Menu[Nivel],Tabla_Menu[[#This Row],[Nivel]]))</calculatedColumnFormula>
       <totalsRowFormula>COUNTIF(Tabla_Menu[N Sub],"&lt;&gt;0")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Nivel" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Nivel" dataDxfId="40" totalsRowDxfId="39">
       <calculatedColumnFormula>IFERROR(INDIRECT(Tabla_Menu[[#This Row],[Nivel 1]]&amp;IDIOMA),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Nombre" dataDxfId="33" totalsRowDxfId="32">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Nombre" dataDxfId="38" totalsRowDxfId="37">
       <calculatedColumnFormula>IFERROR(INDIRECT(Tabla_Menu[[#This Row],[Nivel 2]]&amp;IDIOMA)&amp;IF(Tabla_Menu[[#This Row],[Nivel]]="",""," "&amp;Tabla_Menu[[#This Row],['[Teclas']]]),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="On Action" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="Face Id" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Begin Group" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="Nivel 1" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="Nivel 2" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="Teclas" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="HOJAS NO MUESTRA" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="N/A" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="On Action" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="Face Id" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Begin Group" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="Nivel 1" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="Nivel 2" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="Teclas" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="HOJAS NO MUESTRA" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="N/A" dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>IF(OR(Tabla_Menu[[#This Row],[Nivel]]="",IFERROR(SEARCH(MID(CELL("nombrearchivo"),FIND(".xlsm]",CELL("nombrearchivo"),1)+6,100),Tabla_Menu[[#This Row],[HOJAS NO MUESTRA]],1),0)&gt;0),"N/A","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="Num N/A" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="Num N/A" dataDxfId="20" totalsRowDxfId="19">
       <calculatedColumnFormula>IF(Tabla_Menu[[#This Row],[N/A]]="",,COUNTIF(Tabla_Menu[Nivel &amp; Incluir],Tabla_Menu[[#This Row],[Nivel &amp; Incluir]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="Nivel &amp; Incluir" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="Nivel &amp; Incluir" dataDxfId="18" totalsRowDxfId="17">
       <calculatedColumnFormula>Tabla_Menu[[#This Row],[Nivel]]&amp;Tabla_Menu[[#This Row],[N/A]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="[Teclas]" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="[Teclas]" dataDxfId="16" totalsRowDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="Tabla_UCA" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabla_Comandos" displayName="Tabla_Comandos" ref="U37:W44" totalsRowCount="1" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="6" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabla_Comandos" displayName="Tabla_Comandos" ref="U37:W44" totalsRowCount="1" headerRowDxfId="14" dataDxfId="13" totalsRowDxfId="11" tableBorderDxfId="12">
   <autoFilter ref="U37:W43" xr:uid="{00000000-0009-0000-0100-00000A000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="CommandBars" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="CommandBars" totalsRowFunction="custom" dataDxfId="10" totalsRowDxfId="9">
       <totalsRowFormula>COUNTA(Tabla_Comandos[CommandBars])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Cambio" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Activa/Des" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Cambio" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Activa/Des" dataDxfId="6" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -20882,88 +20874,88 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabla_EN" displayName="Tabla_EN" ref="A4:AI5" totalsRowShown="0" headerRowDxfId="117" dataDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabla_EN" displayName="Tabla_EN" ref="A4:AI5" totalsRowShown="0" headerRowDxfId="119" dataDxfId="118">
   <autoFilter ref="A4:AI5" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="C1" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="C2" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Columna1" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Columna2" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Descripción" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="FastTest PlugIn - ENSAYO_x000a__x000a_Enunciado de la pregunta" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Formato de la Respuesta_x000a_Requerir texto" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Requerir texto" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Tamaño de la caja de entrada" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Permitir archivos adjuntos" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Archivos adjuntos requeridos" dataDxfId="105"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Plantilla de Respuesta" dataDxfId="104"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0700-00000D000000}" name="Información para el evaluador" dataDxfId="103"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Columna3" dataDxfId="102"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="Columna4" dataDxfId="101"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Columna5" dataDxfId="100"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Columna6" dataDxfId="99"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="Columna7" dataDxfId="98"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="Columna8" dataDxfId="97"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="Columna9" dataDxfId="96"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="Columna10" dataDxfId="95"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="Columna11" dataDxfId="94"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0700-000017000000}" name="Columna12" dataDxfId="93"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0700-000018000000}" name="Columna13" dataDxfId="92"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0700-000019000000}" name="Columna14" dataDxfId="91"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="Columna15" dataDxfId="90"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0700-00001B000000}" name="Columna16" dataDxfId="89"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="Columna17" dataDxfId="88"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0700-00001D000000}" name="Columna18" dataDxfId="87"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0700-00001E000000}" name="Columna19" dataDxfId="86"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0700-00001F000000}" name="Columna20" dataDxfId="85"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0700-000020000000}" name="Columna21" dataDxfId="84"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0700-000021000000}" name="Columna22" dataDxfId="83"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0700-000022000000}" name="Columna23" dataDxfId="82"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0700-000023000000}" name="Imagen" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="C1" dataDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="C2" dataDxfId="116"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Columna1" dataDxfId="115"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Columna2" dataDxfId="114"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Descripción" dataDxfId="113"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="FastTest PlugIn - ENSAYO_x000a__x000a_Enunciado de la pregunta" dataDxfId="112"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Formato de la Respuesta_x000a_Requerir texto" dataDxfId="111"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Requerir texto" dataDxfId="110"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Tamaño de la caja de entrada" dataDxfId="109"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Permitir archivos adjuntos" dataDxfId="108"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Archivos adjuntos requeridos" dataDxfId="107"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Plantilla de Respuesta" dataDxfId="106"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0700-00000D000000}" name="Información para el evaluador" dataDxfId="105"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Columna3" dataDxfId="104"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="Columna4" dataDxfId="103"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0700-000010000000}" name="Columna5" dataDxfId="102"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0700-000011000000}" name="Columna6" dataDxfId="101"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0700-000012000000}" name="Columna7" dataDxfId="100"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0700-000013000000}" name="Columna8" dataDxfId="99"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0700-000014000000}" name="Columna9" dataDxfId="98"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0700-000015000000}" name="Columna10" dataDxfId="97"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0700-000016000000}" name="Columna11" dataDxfId="96"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0700-000017000000}" name="Columna12" dataDxfId="95"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0700-000018000000}" name="Columna13" dataDxfId="94"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0700-000019000000}" name="Columna14" dataDxfId="93"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0700-00001A000000}" name="Columna15" dataDxfId="92"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0700-00001B000000}" name="Columna16" dataDxfId="91"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0700-00001C000000}" name="Columna17" dataDxfId="90"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0700-00001D000000}" name="Columna18" dataDxfId="89"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0700-00001E000000}" name="Columna19" dataDxfId="88"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0700-00001F000000}" name="Columna20" dataDxfId="87"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0700-000020000000}" name="Columna21" dataDxfId="86"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0700-000021000000}" name="Columna22" dataDxfId="85"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0700-000022000000}" name="Columna23" dataDxfId="84"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0700-000023000000}" name="Imagen" dataDxfId="83"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabla_CL" displayName="Tabla_CL" ref="A4:AI5" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabla_CL" displayName="Tabla_CL" ref="A4:AI5" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
   <autoFilter ref="A4:AI5" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="C1" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="C2" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Columna1" dataDxfId="76"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Columna2" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Descripcion" dataDxfId="74"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Enunciado" dataDxfId="73"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Ancho RC" dataDxfId="72"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="Columna3" dataDxfId="71"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Ancho IM" dataDxfId="70"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Columna5" dataDxfId="69"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Columna6" dataDxfId="68"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Columna7" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0800-00000D000000}" name="Columna8" dataDxfId="66"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Columna9" dataDxfId="65"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0800-00000F000000}" name="Columna10" dataDxfId="64"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Columna11" dataDxfId="63"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="Columna12" dataDxfId="62"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0800-000012000000}" name="Columna13" dataDxfId="61"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0800-000013000000}" name="Columna14" dataDxfId="60"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0800-000014000000}" name="Columna15" dataDxfId="59"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0800-000015000000}" name="Columna16" dataDxfId="58"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0800-000016000000}" name="Columna17" dataDxfId="57"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0800-000017000000}" name="Columna18" dataDxfId="56"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0800-000018000000}" name="Columna19" dataDxfId="55"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0800-000019000000}" name="Columna20" dataDxfId="54"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0800-00001A000000}" name="Columna21" dataDxfId="53"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0800-00001B000000}" name="Columna22" dataDxfId="52"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0800-00001C000000}" name="Columna23" dataDxfId="51"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0800-00001D000000}" name="Columna24" dataDxfId="50"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0800-00001E000000}" name="Columna25" dataDxfId="49"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0800-00001F000000}" name="Pista 1" dataDxfId="48"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0800-000020000000}" name="Pista 2" dataDxfId="47"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0800-000021000000}" name="Pista 3" dataDxfId="46"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0800-000022000000}" name="Pista 4" dataDxfId="45"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0800-000023000000}" name="Imagen" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="C1" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="C2" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Columna1" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Columna2" dataDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Descripcion" dataDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Enunciado" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Ancho RC" dataDxfId="74"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="Columna3" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="Ancho IM" dataDxfId="72"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="Columna5" dataDxfId="71"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0800-00000B000000}" name="Columna6" dataDxfId="70"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0800-00000C000000}" name="Columna7" dataDxfId="69"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0800-00000D000000}" name="Columna8" dataDxfId="68"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0800-00000E000000}" name="Columna9" dataDxfId="67"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0800-00000F000000}" name="Columna10" dataDxfId="66"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0800-000010000000}" name="Columna11" dataDxfId="65"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0800-000011000000}" name="Columna12" dataDxfId="64"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0800-000012000000}" name="Columna13" dataDxfId="63"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0800-000013000000}" name="Columna14" dataDxfId="62"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0800-000014000000}" name="Columna15" dataDxfId="61"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0800-000015000000}" name="Columna16" dataDxfId="60"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0800-000016000000}" name="Columna17" dataDxfId="59"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0800-000017000000}" name="Columna18" dataDxfId="58"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0800-000018000000}" name="Columna19" dataDxfId="57"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0800-000019000000}" name="Columna20" dataDxfId="56"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0800-00001A000000}" name="Columna21" dataDxfId="55"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0800-00001B000000}" name="Columna22" dataDxfId="54"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0800-00001C000000}" name="Columna23" dataDxfId="53"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0800-00001D000000}" name="Columna24" dataDxfId="52"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0800-00001E000000}" name="Columna25" dataDxfId="51"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0800-00001F000000}" name="Pista 1" dataDxfId="50"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0800-000020000000}" name="Pista 2" dataDxfId="49"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0800-000021000000}" name="Pista 3" dataDxfId="48"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0800-000022000000}" name="Pista 4" dataDxfId="47"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0800-000023000000}" name="Imagen" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22160,7 +22152,7 @@
     </row>
     <row r="47" spans="1:19" ht="5.0999999999999996" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="B4ZtyPI8lv6/MGOS3+9a5fUlVKn8W7m5tc5qom7GwcpKDO4mxFaT3Eq647jn8+lsT+zoaLPf06hAUqFkuo98DA==" saltValue="Oavj1BI2LOGiAwJ94csGEA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hgvpnUQ7b9+8y0nx5HU2WCVmld006ea5Pyz5KAGqrSL6/G8GPWD7dedCcX1aTIvjn20/MGgRGFnFGf02ynowjw==" saltValue="bEc5su5nGa78VoiOxURzLw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="42">
     <mergeCell ref="A1:A9"/>
     <mergeCell ref="A11:A13"/>
@@ -22205,7 +22197,7 @@
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A11:A13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$A$39:$A$46</formula1>
     </dataValidation>
@@ -22215,11 +22207,12 @@
     <hyperlink ref="I9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="O1:P1" r:id="rId3" display="GENERAR BANCO DE PREGUNTAS PARA MOODLE Versión 3.8" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="H5:K5" r:id="rId4" display="MILAGROS HUERTA GÓMEZ DE MERODIO" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I5:L5" r:id="rId5" display="MILAGROS HUERTA GÓMEZ DE MERODIO" xr:uid="{32F1971F-D4AA-41CB-BEBA-EA61FF5F6479}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -27353,13 +27346,13 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="EFvDi3MSRW73NdIsYvAsc+BhgNAxKxcPxTt3ACKCjR73QNbhqIfRpAgCELXZUjGGqLKgcIubArfstFoT9O9iow==" saltValue="M4mqjZOIoId7mfBIEVvyPQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="F3:F53 F55">
-    <cfRule type="duplicateValues" dxfId="43" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="duplicateValues" dxfId="42" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56:F66">
-    <cfRule type="duplicateValues" dxfId="41" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W38:W43 X3:X29" xr:uid="{00000000-0002-0000-0900-000000000000}">
@@ -27467,7 +27460,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!C24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - OPCIÓN MÚLTIPLE 1R 
+        <v>FastTest PlugIn - V8.3  - OPCIÓN MÚLTIPLE 1R 
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -27718,7 +27711,7 @@
       <c r="AI5" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="H8X283uQNnC7gz1Hhpsr/k1uCOIh7uV2enl6jFOPL2SqtqDAAalnBNVWAMjnI7q9Mu5hfRsvfdj1kuX2tP8haQ==" saltValue="Wn+T8GSKXuKOh67tmc7rig==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -27816,7 +27809,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!E24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - OPCIÓN MÚLTIPLE +R 
+        <v>FastTest PlugIn - V8.3  - OPCIÓN MÚLTIPLE +R 
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -28071,7 +28064,7 @@
       <c r="AI5" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ERBY/PTf+dZQ++2KEpITtNytAqMp+wAXbFbwRFolNIeyMBBbXIaNYTiDpbKpg6E8If7o1MCA0Q8xJbRoGPUZ5w==" saltValue="qx18K537RiTwcH8K85vvLw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -28161,7 +28154,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!G24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - VERDADERO/FALSO
+        <v>FastTest PlugIn - V8.3  - VERDADERO/FALSO
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -28362,7 +28355,7 @@
       <c r="AI5" s="66"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dVkVd6fI+jzBf8u1+/VP4Ng8RqSClfneuUJVS3Zqb2oqPuAHZSM8UJJhPVpP+9hNF8Op4In2F3YoDEDQhSzWVA==" saltValue="GF30sTwjN9qAIgZXdQ40Fw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -28456,7 +28449,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!I24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - EMPAREJAR
+        <v>FastTest PlugIn - V8.3  - EMPAREJAR
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -28723,7 +28716,7 @@
       <c r="AI5" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NXSjViADsEhsSPzF3dgHHj6miypefKCRBTiqLmxRci9fwD/iX5tpWEmkbDV+uWHcaPXobc6waz6gKMDib2PnFg==" saltValue="POlr9CWdSVXyh5bUk+dMyg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -28826,7 +28819,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!K24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - RESPUESTA CORTA
+        <v>FastTest PlugIn - V8.3  - RESPUESTA CORTA
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -29095,7 +29088,7 @@
       <c r="AI5" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mm5cZceM5w7XZcV2SOekDIICsBn5c0LYQ4yT2KEAXYDJgPoU1Kmpgav8/obtOBNWUzr4k7+tOOYf6TGvdgKJIA==" saltValue="3Jx//6wN+ppfh3/jT43trg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -29189,7 +29182,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!M24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - PALABRA PERDIDA
+        <v>FastTest PlugIn - V8.3  - PALABRA PERDIDA
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="117" t="str">
@@ -29481,7 +29474,7 @@
       <c r="AI5" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sEKH96XAJodnKVCQc0jCeDCCbeSMPKabK32+RcqGSVeYG4/1hQXY3TWQkYorfLK4G10Lw67aVf9Z8pw6wq32ag==" saltValue="ho2Y56xcM/s3igiJwne8ng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -29578,7 +29571,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!O24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - ENSAYO
+        <v>FastTest PlugIn - V8.3  - ENSAYO
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="55" t="str">
@@ -29782,12 +29775,12 @@
       <c r="AI5" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tv4T8jIp/0uneJGuqGN/pU3Vs0rsRtonJP1W8okTN8UYG6pdTOXOtMPYhN1m600I7M36ItxW+p5sHVPdazA0hA==" saltValue="Ob8LGkCFfnGxwZEW0HbWKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <conditionalFormatting sqref="G5:K5">
-    <cfRule type="cellIs" dxfId="119" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29881,7 +29874,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!Q24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - CLOZE
+        <v>FastTest PlugIn - V8.3  - CLOZE
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="133" t="str">
@@ -30080,7 +30073,7 @@
       <c r="AI5" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bbdWd6QPCJhLsv2ArhcLj8cjfN1AVpKdybfX02xB3lOb1rEbhnVufed6aVsJJQloiMrblxuG72/o2i5fCkchmg==" saltValue="R1tr5CKgYUlGNfB5r+J72A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="1">
     <mergeCell ref="A3:B3"/>
   </mergeCells>
